--- a/UnitTestPlan.xlsx
+++ b/UnitTestPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{93D35409-1E23-4B31-881A-246E147CFDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC77A59-22DF-4EF7-B895-36799774334D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9D56D6B0-F959-4F3C-B16D-1A3D136B1B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9D5C4A-BA24-4721-ADC9-D0F512511374}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -217,13 +217,157 @@
   </si>
   <si>
     <t>Expected</t>
+  </si>
+  <si>
+    <t>Triage Agent classifies Critical severity</t>
+  </si>
+  <si>
+    <t>Paste a bug report containing "production is down" and submit</t>
+  </si>
+  <si>
+    <t>Report contains a Critical-severity keyword</t>
+  </si>
+  <si>
+    <t>Bug is saved with severity = Critical, priority = P0, and a reasoning string listing the matched keyword(s)</t>
+  </si>
+  <si>
+    <t>Triage Agent falls back to Medium on weak signal</t>
+  </si>
+  <si>
+    <t>Paste a cosmetic UI report that happens to contain the word "fail" once, then submit</t>
+  </si>
+  <si>
+    <t>Only a single incidental keyword match, no structural signal</t>
+  </si>
+  <si>
+    <t>Bug is saved with severity = Medium (not High), reasoning explains the signal was too weak to elevate</t>
+  </si>
+  <si>
+    <t>Triage Agent bumps priority on urgent language</t>
+  </si>
+  <si>
+    <t>Paste a High-severity report that also contains "ASAP", then submit</t>
+  </si>
+  <si>
+    <t>Severity is already High and urgency keyword is present</t>
+  </si>
+  <si>
+    <t>Priority is bumped from P1 to P0; severity itself is unchanged</t>
+  </si>
+  <si>
+    <t>Triage Agent classifies affected component</t>
+  </si>
+  <si>
+    <t>Paste a report mentioning "login", "token", and "session"</t>
+  </si>
+  <si>
+    <t>Report contains Authentication-related keywords</t>
+  </si>
+  <si>
+    <t>Bug is saved with component = Authentication</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent parses Python traceback</t>
+  </si>
+  <si>
+    <t>Paste a Python traceback ending in a raised exception, then submit</t>
+  </si>
+  <si>
+    <t>Content contains "Traceback (most recent call last)"</t>
+  </si>
+  <si>
+    <t>Agent output has language = Python, correct exception_type/message, and failure_file/failure_line taken from the last frame</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent parses Java stack trace</t>
+  </si>
+  <si>
+    <t>Paste a Java stack trace with "Exception in thread", then submit</t>
+  </si>
+  <si>
+    <t>Content matches Java stack trace signature</t>
+  </si>
+  <si>
+    <t>Agent output has language = Java with correct exception_type and failure point</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent parses JS/Node runtime error</t>
+  </si>
+  <si>
+    <t>Paste a Node console error with "Uncaught TypeError", then submit</t>
+  </si>
+  <si>
+    <t>Content matches JS/Node error signature</t>
+  </si>
+  <si>
+    <t>Agent output has language = JavaScript, correct exception_type, and file:line:col taken from inside parentheses</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent handles unstructured report</t>
+  </si>
+  <si>
+    <t>Paste plain-English bug description with no stack trace, then submit</t>
+  </si>
+  <si>
+    <t>Content has no recognizable stack trace pattern</t>
+  </si>
+  <si>
+    <t>Agent output has language = null and reasoning = "no recognized stack trace signature; treated as unstructured report"</t>
+  </si>
+  <si>
+    <t>Orchestrator runs both agents on submission</t>
+  </si>
+  <si>
+    <t>Submit a bug report via paste or upload</t>
+  </si>
+  <si>
+    <t>Any valid bug report is submitted</t>
+  </si>
+  <si>
+    <t>Both Triage Agent and Log Analysis Agent run automatically; combined output is included in the response</t>
+  </si>
+  <si>
+    <t>Combined analysis persisted and retrievable</t>
+  </si>
+  <si>
+    <t>GET /api/bugs/{id}/analysis after submitting a bug</t>
+  </si>
+  <si>
+    <t>Bug has already been analyzed and saved</t>
+  </si>
+  <si>
+    <t>Full combined_json (triage + log_analysis) is returned, matching what was stored at submission time</t>
+  </si>
+  <si>
+    <t>Analysis endpoint returns 404 when missing</t>
+  </si>
+  <si>
+    <t>GET /api/bugs/{id}/analysis for a bug that has no analysis record</t>
+  </si>
+  <si>
+    <t>No AgentAnalysis row exists for the given bug</t>
+  </si>
+  <si>
+    <t>"No agent analysis found for this bug." error returned</t>
+  </si>
+  <si>
+    <t>validate_agents.py reports accuracy on seeded dataset</t>
+  </si>
+  <si>
+    <t>Run validate_agents.py against the seeded dataset of varied bug report styles</t>
+  </si>
+  <si>
+    <t>Seeded dataset covers Python, Java, JS, plain-text, and cosmetic/UI reports with known-correct labels</t>
+  </si>
+  <si>
+    <t>Script prints per-agent accuracy percentage and lists any misclassified samples</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -244,6 +388,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF003366"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -259,7 +416,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -295,11 +452,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -307,11 +478,32 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{9FB23293-3104-4132-B55C-0ABE6C25F448}"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -347,20 +539,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -375,8 +553,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4D73866-2CAE-404B-8875-39C90D553908}" name="Table1" displayName="Table1" ref="A1:F16" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:F16" xr:uid="{C4D73866-2CAE-404B-8875-39C90D553908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4D73866-2CAE-404B-8875-39C90D553908}" name="Table1" displayName="Table1" ref="A1:F28" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:F28" xr:uid="{C4D73866-2CAE-404B-8875-39C90D553908}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{63203D93-E3E9-45A3-BA19-5E29FF476F82}" name="Sl: No:"/>
     <tableColumn id="2" xr3:uid="{16AB9744-4A36-43B7-BAED-6D3015B77767}" name="Test Case Name"/>
@@ -686,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
@@ -1017,6 +1195,246 @@
         <v>61</v>
       </c>
     </row>
+    <row r="17" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="77.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="62" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="77.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="77.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/UnitTestPlan.xlsx
+++ b/UnitTestPlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{9D56D6B0-F959-4F3C-B16D-1A3D136B1B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9D5C4A-BA24-4721-ADC9-D0F512511374}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A310E0B4-F5FE-4807-B7B5-A481FD4277C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7405777C-9BEF-4835-9603-B982274B6F25}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="197">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -361,6 +361,267 @@
   </si>
   <si>
     <t>Script prints per-agent accuracy percentage and lists any misclassified samples</t>
+  </si>
+  <si>
+    <t>Root Cause Agent retrieves historical matches via TF-IDF</t>
+  </si>
+  <si>
+    <t>Paste a bug report similar to a seeded historical defect, then submit</t>
+  </si>
+  <si>
+    <t>Report text overlaps strongly with a historical defect symptom_text</t>
+  </si>
+  <si>
+    <t>Root cause hypothesis references the matching defect_id  and confidence</t>
+  </si>
+  <si>
+    <t>Root Cause Agent falls back on weak similarity</t>
+  </si>
+  <si>
+    <t>Paste a bug report with only partial overlap to any historical defect, then submit</t>
+  </si>
+  <si>
+    <t>Best match strength is in the corresponding band</t>
+  </si>
+  <si>
+    <t>Hypothesis is flagged as a "weak hypothesis pending engineer review" with moderate confidence</t>
+  </si>
+  <si>
+    <t>Root Cause Agent falls back to heuristic with no KB match</t>
+  </si>
+  <si>
+    <t>Paste a bug report with no overlap to the historical KB but containing a clear exception type, then submit</t>
+  </si>
+  <si>
+    <t>Hypothesis is derived from Log Analysis exception_type and Triage component, confidence moderate.35</t>
+  </si>
+  <si>
+    <t>Root Cause Agent handles empty historical KB</t>
+  </si>
+  <si>
+    <t>Submit a bug report when HistoricalDefect table has zero rows</t>
+  </si>
+  <si>
+    <t>No historical defects exist in the database</t>
+  </si>
+  <si>
+    <t>Hypothesis states no KB is available, confidence is zero, evidence = empty list</t>
+  </si>
+  <si>
+    <t>Root Cause Agent returns supporting evidence list</t>
+  </si>
+  <si>
+    <t>Paste a bug report matching multiple historical defects, then submit</t>
+  </si>
+  <si>
+    <t>Report overlaps with multiple historical defects</t>
+  </si>
+  <si>
+    <t>Evidence list contains up to 3 defects with defect_id, title, similarity, and root_cause</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent finds match in historical KB</t>
+  </si>
+  <si>
+    <t>Paste a bug report closely matching a seeded historical defect, then submit</t>
+  </si>
+  <si>
+    <t>Report text is highly similar to a KB entry</t>
+  </si>
+  <si>
+    <t>Duplicate match returned with source = historical_kb, correct similarity_pct, and resolution_summary</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent finds match in prior submissions</t>
+  </si>
+  <si>
+    <t>Submit two similar bug reports back to back</t>
+  </si>
+  <si>
+    <t>A prior live submission exists with similar content</t>
+  </si>
+  <si>
+    <t>Second submission returns a duplicate match with source = prior_submission and the correct bug_id</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent filters low-similarity noise</t>
+  </si>
+  <si>
+    <t>Paste a bug report unrelated to any KB entry or prior submission, then submit</t>
+  </si>
+  <si>
+    <t>All candidate match strength are in the corresponding band</t>
+  </si>
+  <si>
+    <t>Duplicate matches list is empty, reasoning explains the threshold was not met</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent excludes the bug itself</t>
+  </si>
+  <si>
+    <t>Re-analyze an existing bug submission</t>
+  </si>
+  <si>
+    <t>exclude_bug_db_id is passed for the current bug</t>
+  </si>
+  <si>
+    <t>The bug being analyzed never appears as its own duplicate match</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent handles empty corpus</t>
+  </si>
+  <si>
+    <t>Submit the very first bug report when KB and prior submissions are both empty</t>
+  </si>
+  <si>
+    <t>No historical KB entries and no prior submissions exist</t>
+  </si>
+  <si>
+    <t>Duplicate matches list is empty with reasoning "No historical KB entries or prior submissions to compare against."</t>
+  </si>
+  <si>
+    <t>Remediation Agent grounds fix in strong duplicate match</t>
+  </si>
+  <si>
+    <t>Submit a bug report that produces a duplicate match and a real resolution summary</t>
+  </si>
+  <si>
+    <t>A strong duplicate match with a valid resolution_summary exists</t>
+  </si>
+  <si>
+    <t>Remediation summary and first step reference the matched duplicate's resolution; sources list includes the duplicate reference</t>
+  </si>
+  <si>
+    <t>Remediation Agent grounds fix in root cause when no strong duplicate</t>
+  </si>
+  <si>
+    <t>Submit a bug report with high root cause confidence but no strong duplicate match</t>
+  </si>
+  <si>
+    <t>Root cause confidence is high, duplicate match is weak or absent</t>
+  </si>
+  <si>
+    <t>Remediation step addresses the root cause hypothesis directly; sources include root_cause_evidence or heuristic tag</t>
+  </si>
+  <si>
+    <t>Remediation Agent falls back to investigation steps</t>
+  </si>
+  <si>
+    <t>Submit a bug report with low root cause confidence and no strong duplicate match</t>
+  </si>
+  <si>
+    <t>Both root cause confidence and duplicate similarity are low</t>
+  </si>
+  <si>
+    <t>First remediation step recommends reproducing the issue and adding logging before attempting a fix</t>
+  </si>
+  <si>
+    <t>Remediation Agent appends best-practice playbook</t>
+  </si>
+  <si>
+    <t>Submit a bug report classified under a known component (e.g., Authentication)</t>
+  </si>
+  <si>
+    <t>Triage component matches one of the defined playbooks</t>
+  </si>
+  <si>
+    <t>Remediation steps include the component-specific best-practice steps, with sources tagged best_practice_playbook</t>
+  </si>
+  <si>
+    <t>Remediation Agent de-duplicates repeated steps</t>
+  </si>
+  <si>
+    <t>Submit a bug report where duplicate and root cause context produce overlapping recommendations</t>
+  </si>
+  <si>
+    <t>Multiple context sources suggest the same remediation text</t>
+  </si>
+  <si>
+    <t>Final steps list contains no duplicate entries while preserving priority order</t>
+  </si>
+  <si>
+    <t>Remediation Agent confidence never exceeds input confidence</t>
+  </si>
+  <si>
+    <t>Submit a bug report with a moderate duplicate similarity and moderate root cause confidence</t>
+  </si>
+  <si>
+    <t>Both duplicate match strength and root cause confidence are both low</t>
+  </si>
+  <si>
+    <t>Remediation confidence score is capped and does not overstate certainty beyond its inputs</t>
+  </si>
+  <si>
+    <t>Orchestrator runs all 5 agents on submission</t>
+  </si>
+  <si>
+    <t>Triage, Log Analysis, Root Cause, Duplicate Detection, and Remediation agents all run automatically; combined output is included in the response</t>
+  </si>
+  <si>
+    <t>Combined analysis persists all 5 agent outputs</t>
+  </si>
+  <si>
+    <t>Full combined_json includes triage, log_analysis, root_cause, duplicates, and remediation, matching what was stored at submission time</t>
+  </si>
+  <si>
+    <t>Structured Findings Dashboard renders all sections</t>
+  </si>
+  <si>
+    <t>Submit a bug report and view the live preview panel</t>
+  </si>
+  <si>
+    <t>Analysis completes successfully</t>
+  </si>
+  <si>
+    <t>Dashboard shows Triage, Log Analysis, Root Cause, Duplicate Bugs, and Recommendations sections with confidence bars</t>
+  </si>
+  <si>
+    <t>Structured Findings Dashboard shows empty states gracefully</t>
+  </si>
+  <si>
+    <t>Submit a bug report with no historical evidence or duplicate matches</t>
+  </si>
+  <si>
+    <t>Root cause evidence and duplicate matches are both empty</t>
+  </si>
+  <si>
+    <t>Dashboard displays "No supporting historical evidence found." and "No duplicate or closely similar issues found." instead of blank sections</t>
+  </si>
+  <si>
+    <t>History detail modal renders full 5-agent dashboard</t>
+  </si>
+  <si>
+    <t>Click a past submission in the Submission history list</t>
+  </si>
+  <si>
+    <t>Selected bug has a saved AgentAnalysis record</t>
+  </si>
+  <si>
+    <t>Modal opens showing the same 5-section Structured Findings Dashboard as the live preview</t>
+  </si>
+  <si>
+    <t>Dashboard handles submission with no analysis record</t>
+  </si>
+  <si>
+    <t>Open a bug detail whose AgentAnalysis record is missing</t>
+  </si>
+  <si>
+    <t>GET /api/bugs/{id}/analysis returns 404</t>
+  </si>
+  <si>
+    <t>Dashboard shows "No agent analysis available for this submission." without breaking the page</t>
+  </si>
+  <si>
+    <t>GET /api/historical-defects returns seeded KB</t>
+  </si>
+  <si>
+    <t>GET /api/historical-defects</t>
+  </si>
+  <si>
+    <t>HistoricalDefect table has been seeded on startup</t>
+  </si>
+  <si>
+    <t>JSON list of all 10 seeded defects returned with defect_id, title, component, root_cause, resolution_summary, and tags</t>
   </si>
 </sst>
 </file>
@@ -470,7 +731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -482,6 +743,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -864,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
@@ -1435,6 +1699,466 @@
         <v>61</v>
       </c>
     </row>
+    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="77.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="139.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="77.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="155" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="139.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="139.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="155" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="155" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="170.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="108.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="124" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
